--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.672374630878</v>
+        <v>8.884260877517674</v>
       </c>
       <c r="D2" t="n">
-        <v>20.21069573820314</v>
+        <v>3.28423805745801</v>
       </c>
       <c r="E2" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F2" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.86797789267076</v>
+        <v>9.891046407558999</v>
       </c>
       <c r="D3" t="n">
-        <v>36.20790658109734</v>
+        <v>5.883784819428318</v>
       </c>
       <c r="E3" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F3" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.54430247636986</v>
+        <v>8.213449152410103</v>
       </c>
       <c r="D4" t="n">
-        <v>23.79542439676633</v>
+        <v>3.866756464474529</v>
       </c>
       <c r="E4" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F4" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>83.51461403560995</v>
+        <v>13.57112478078662</v>
       </c>
       <c r="D5" t="n">
-        <v>69.38459643337434</v>
+        <v>11.27499692042333</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F5" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.97220705991156</v>
+        <v>6.982983647235629</v>
       </c>
       <c r="D6" t="n">
-        <v>14.73308184941798</v>
+        <v>2.394125800530421</v>
       </c>
       <c r="E6" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F6" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>66.18456998834293</v>
+        <v>10.75499262310573</v>
       </c>
       <c r="D7" t="n">
-        <v>48.71539406053297</v>
+        <v>7.916251534836607</v>
       </c>
       <c r="E7" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F7" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.81391468227091</v>
+        <v>7.282261135869024</v>
       </c>
       <c r="D8" t="n">
-        <v>15.09340356702992</v>
+        <v>2.452678079642362</v>
       </c>
       <c r="E8" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F8" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.75805605381619</v>
+        <v>5.810684108745131</v>
       </c>
       <c r="D9" t="n">
-        <v>22.87405128573035</v>
+        <v>3.717033333931181</v>
       </c>
       <c r="E9" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F9" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.37300748993777</v>
+        <v>4.935613717114887</v>
       </c>
       <c r="D10" t="n">
-        <v>8.008675851155971</v>
+        <v>1.301409825812845</v>
       </c>
       <c r="E10" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F10" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.5790367708169</v>
+        <v>7.731593475257746</v>
       </c>
       <c r="D11" t="n">
-        <v>44.75923244302664</v>
+        <v>7.27337527199183</v>
       </c>
       <c r="E11" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F11" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>93.75449921518408</v>
+        <v>15.23510612246741</v>
       </c>
       <c r="D12" t="n">
-        <v>89.87631141857098</v>
+        <v>14.60490060551778</v>
       </c>
       <c r="E12" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F12" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.75187303810731</v>
+        <v>5.484679368692437</v>
       </c>
       <c r="D13" t="n">
-        <v>35.59580968910652</v>
+        <v>5.784319074479809</v>
       </c>
       <c r="E13" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F13" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.88084184559728</v>
+        <v>1.930636799909558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.96044681732863</v>
+        <v>2.268572607815903</v>
       </c>
       <c r="E14" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F14" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6.442426032060603</v>
+        <v>1.046894230209848</v>
       </c>
       <c r="D15" t="n">
-        <v>8.389373101229236</v>
+        <v>1.363273128949751</v>
       </c>
       <c r="E15" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F15" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.04399168513351</v>
+        <v>3.582148648834195</v>
       </c>
       <c r="D16" t="n">
-        <v>23.5978427646108</v>
+        <v>3.834649449249254</v>
       </c>
       <c r="E16" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F16" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.8267978743075</v>
+        <v>6.309354654574969</v>
       </c>
       <c r="D17" t="n">
-        <v>37.9356903343534</v>
+        <v>6.164549679332427</v>
       </c>
       <c r="E17" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F17" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>38.90432017759247</v>
+        <v>6.321952028858777</v>
       </c>
       <c r="D18" t="n">
-        <v>40.15821398353673</v>
+        <v>6.52570977232472</v>
       </c>
       <c r="E18" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F18" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>51.63299884154692</v>
+        <v>8.390362311751375</v>
       </c>
       <c r="D19" t="n">
-        <v>52.71160978092318</v>
+        <v>8.565636589400018</v>
       </c>
       <c r="E19" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F19" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>55.95594928221572</v>
+        <v>9.092841758360056</v>
       </c>
       <c r="D20" t="n">
-        <v>56.79154081978565</v>
+        <v>9.228625383215167</v>
       </c>
       <c r="E20" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F20" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>45.4058908876884</v>
+        <v>7.378457269249365</v>
       </c>
       <c r="D21" t="n">
-        <v>46.15868488920286</v>
+        <v>7.500786294495465</v>
       </c>
       <c r="E21" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F21" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>44.89782737948324</v>
+        <v>7.295896949166027</v>
       </c>
       <c r="D22" t="n">
-        <v>43.88688297190188</v>
+        <v>7.131618482934055</v>
       </c>
       <c r="E22" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F22" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>36.67044429864105</v>
+        <v>5.958947198529171</v>
       </c>
       <c r="D23" t="n">
-        <v>35.33127984542716</v>
+        <v>5.741332974881914</v>
       </c>
       <c r="E23" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F23" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>48.75838756579501</v>
+        <v>7.92323797944169</v>
       </c>
       <c r="D24" t="n">
-        <v>46.55860857927289</v>
+        <v>7.565773894131844</v>
       </c>
       <c r="E24" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F24" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>51.02917183876789</v>
+        <v>8.292240423799782</v>
       </c>
       <c r="D25" t="n">
-        <v>49.11675362017891</v>
+        <v>7.981472463279074</v>
       </c>
       <c r="E25" t="n">
-        <v>18.9070363196753</v>
+        <v>3.072393401947237</v>
       </c>
       <c r="F25" t="n">
-        <v>19.43653615275043</v>
+        <v>3.158437124821945</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
